--- a/backend/LPG testing/carbon-credits-{template}.xlsx
+++ b/backend/LPG testing/carbon-credits-{template}.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{4007055A-7FB8-4884-B6C5-AD44DAA53F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D197141-1F65-48C0-89B0-9F906D58182C}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{4007055A-7FB8-4884-B6C5-AD44DAA53F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44AD9C85-B674-423A-9687-93095E623D13}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>Units</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Potential income from Carbon Credits in the {model} Plan - right</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Inputs</t>
@@ -221,10 +218,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -501,13 +494,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>8</v>
+      <c r="C1" s="7">
+        <v>2020</v>
       </c>
       <c r="D1" s="7">
         <v>2021</v>
